--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_172_R18.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_172_R18.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3961</v>
+        <v>2.9166</v>
       </c>
       <c r="E2" t="n">
-        <v>1.0277</v>
+        <v>1.2204</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3684</v>
+        <v>1.6962</v>
       </c>
       <c r="G2" t="n">
         <v>1.8355</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7256</v>
+        <v>1.2461</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4525</v>
+        <v>0.6451</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2731</v>
+        <v>0.601</v>
       </c>
       <c r="V2" t="n">
         <v>-1.3247</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. BOSTON JR.</t>
+          <t>T. HORTON TUCKER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8404</v>
+        <v>1.6169</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3882</v>
+        <v>0.8542</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2286</v>
+        <v>0.7627</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.3729</v>
+        <v>1.4838</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1655</v>
+        <v>1.8149</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2074</v>
+        <v>-0.3311</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1776</v>
+        <v>2.1056</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0672</v>
+        <v>1.6405</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1104</v>
+        <v>0.465</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5505</v>
+        <v>-0.6218</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2327</v>
+        <v>0.1744</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3178</v>
+        <v>-0.7961</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.3917</v>
+        <v>-3.7112</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2133</v>
+        <v>-0.4393</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8259</v>
+        <v>0.0318</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3875</v>
+        <v>-0.4711</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>2.428</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.428</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. COLSON</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6153</v>
+        <v>1.5304</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0345</v>
+        <v>0.7914</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6498</v>
+        <v>0.739</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0494</v>
+        <v>2.5487</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6532</v>
+        <v>-0.3757</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7026</v>
+        <v>2.9244</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9443</v>
+        <v>2.9062</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9075</v>
+        <v>-0.3929</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0368</v>
+        <v>3.299</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9937</v>
+        <v>-0.3575</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2543</v>
+        <v>0.0171</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.3746</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9278</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2631</v>
+        <v>0.8373</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7468</v>
+        <v>0.4367</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4837</v>
+        <v>0.4007</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>B. COLSON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5806</v>
+        <v>0.7339</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2449</v>
+        <v>0.3194</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3358</v>
+        <v>0.4145</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5487</v>
+        <v>-0.0494</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3757</v>
+        <v>0.6532</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9244</v>
+        <v>-0.7026</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9062</v>
+        <v>0.9443</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3929</v>
+        <v>0.9075</v>
       </c>
       <c r="L5" t="n">
-        <v>3.299</v>
+        <v>0.0368</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3575</v>
+        <v>-0.9937</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0171</v>
+        <v>-0.2543</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3746</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.5515</v>
+        <v>-0.232</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1125</v>
+        <v>-0.1445</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1098</v>
+        <v>-0.393</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0026</v>
+        <v>0.2484</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. HORTON TUCKER</t>
+          <t>W. BALDWIN IV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3811</v>
+        <v>0.3304</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1897</v>
+        <v>-1.078</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1914</v>
+        <v>1.4083</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4838</v>
+        <v>-1.3771</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8149</v>
+        <v>-0.6846</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3311</v>
+        <v>-0.6925</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1056</v>
+        <v>-1.8706</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6405</v>
+        <v>-1.71</v>
       </c>
       <c r="L6" t="n">
-        <v>0.465</v>
+        <v>-0.1607</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6218</v>
+        <v>0.4936</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1744</v>
+        <v>1.0254</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7961</v>
+        <v>-0.5319</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.8556</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.7112</v>
+        <v>-2.5515</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.6751</v>
+        <v>-0.0452</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.4086</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0425</v>
+        <v>0.3633</v>
       </c>
       <c r="V6" t="n">
-        <v>2.428</v>
+        <v>2.6805</v>
       </c>
       <c r="W6" t="n">
-        <v>2.428</v>
+        <v>3.7527</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W. BALDWIN IV</t>
+          <t>B. BOSTON JR.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1287</v>
+        <v>0.3014</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.078</v>
+        <v>-0.86</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2067</v>
+        <v>1.1614</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3771</v>
+        <v>-0.3729</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6846</v>
+        <v>-0.1655</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6925</v>
+        <v>-0.2074</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.8706</v>
+        <v>0.1776</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.71</v>
+        <v>0.0672</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1607</v>
+        <v>0.1104</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4936</v>
+        <v>-0.5505</v>
       </c>
       <c r="N7" t="n">
-        <v>1.0254</v>
+        <v>-0.2327</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5319</v>
+        <v>-0.3178</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.5515</v>
+        <v>-1.3917</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2469</v>
+        <v>0.6743</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4086</v>
+        <v>0.3541</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1617</v>
+        <v>0.3203</v>
       </c>
       <c r="V7" t="n">
-        <v>2.6805</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.7527</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5099</v>
+        <v>-0.4346</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5668</v>
+        <v>-2.2562</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0568</v>
+        <v>1.8216</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2928</v>
@@ -1078,13 +1078,13 @@
         <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5663</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1845</v>
+        <v>0.1261</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7508</v>
+        <v>0.5155</v>
       </c>
       <c r="V8" t="n">
         <v>1.6083</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0054</v>
+        <v>-0.9718</v>
       </c>
       <c r="E9" t="n">
         <v>-0.9021</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1033</v>
+        <v>-0.0697</v>
       </c>
       <c r="G9" t="n">
         <v>-1.1851</v>
@@ -1156,13 +1156,13 @@
         <v>0.232</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0523</v>
+        <v>-0.0187</v>
       </c>
       <c r="T9" t="n">
         <v>-0.1494</v>
       </c>
       <c r="U9" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.1307</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. BIRCH</t>
+          <t>A. BACOT JR.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1818</v>
+        <v>-2.1004</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8216</v>
+        <v>-3.0091</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3602</v>
+        <v>0.9087</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8554</v>
+        <v>-1.8056</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3469</v>
+        <v>-1.5546</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5085</v>
+        <v>-0.251</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.39</v>
+        <v>-1.7197</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4636</v>
+        <v>-1.5223</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0736</v>
+        <v>-0.1975</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4655</v>
+        <v>-0.0859</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8834</v>
+        <v>-0.0323</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5821</v>
+        <v>-0.0535</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.6237</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.5515</v>
+        <v>-1.3917</v>
       </c>
       <c r="R10" t="n">
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>2.0137</v>
+        <v>0.1691</v>
       </c>
       <c r="T10" t="n">
-        <v>1.8363</v>
+        <v>0.1024</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1775</v>
+        <v>0.0668</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. BACOT JR.</t>
+          <t>K. BIRCH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9989</v>
+        <v>-2.3031</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7732</v>
+        <v>-1.8085</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7743</v>
+        <v>-0.4946</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8056</v>
+        <v>-1.8554</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5546</v>
+        <v>-1.3469</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.251</v>
+        <v>-0.5085</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.7197</v>
+        <v>-0.39</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.5223</v>
+        <v>-0.4636</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1975</v>
+        <v>0.0736</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0859</v>
+        <v>-1.4655</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0323</v>
+        <v>-0.8834</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0535</v>
+        <v>-0.5821</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4639</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.3917</v>
+        <v>-2.5515</v>
       </c>
       <c r="R11" t="n">
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2706</v>
+        <v>0.8924</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3383</v>
+        <v>0.8494</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0677</v>
+        <v>0.0431</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2462</v>
+        <v>1.6197</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.102100000000001</v>
+        <v>-6.7285</v>
       </c>
       <c r="F12" t="n">
-        <v>8.3483</v>
+        <v>8.348100000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-2.0703</v>
@@ -1381,7 +1381,7 @@
         <v>-4.515899999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>-5.798699999999999</v>
+        <v>-5.7987</v>
       </c>
       <c r="Q12" t="n">
         <v>-17.3965</v>
@@ -1390,16 +1390,16 @@
         <v>11.5977</v>
       </c>
       <c r="S12" t="n">
-        <v>3.4396</v>
+        <v>3.813099999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2213</v>
+        <v>1.5946</v>
       </c>
       <c r="U12" t="n">
-        <v>2.2186</v>
+        <v>2.2187</v>
       </c>
       <c r="V12" t="n">
-        <v>5.675699999999999</v>
+        <v>5.6757</v>
       </c>
       <c r="W12" t="n">
         <v>7.284</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.8033</v>
+        <v>4.426</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0414</v>
+        <v>3.3953</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7619</v>
+        <v>1.0307</v>
       </c>
       <c r="G13" t="n">
         <v>4.0053</v>
@@ -1468,13 +1468,13 @@
         <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1299</v>
+        <v>-0.5072</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7389</v>
+        <v>-0.3851</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.391</v>
+        <v>-0.1221</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6469</v>
+        <v>1.4452</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9517</v>
+        <v>0.5516</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3049</v>
+        <v>0.8935999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6251</v>
+        <v>1.8015</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.9832</v>
+        <v>0.9785</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3581</v>
+        <v>0.823</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1352</v>
+        <v>2.1553</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.3929</v>
+        <v>0.9075</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2576</v>
+        <v>1.2479</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4899</v>
+        <v>-0.3538</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5904</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1005</v>
+        <v>-0.4248</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5515</v>
+        <v>0.6959</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5515</v>
+        <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3984</v>
+        <v>-0.7685999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0148</v>
+        <v>-0.4439</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6163</v>
+        <v>-0.3246</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.2836</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.7501</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.496</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6696</v>
+        <v>-1.2045</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8264</v>
+        <v>2.1365</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8015</v>
+        <v>-0.3585</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9785</v>
+        <v>-3.1958</v>
       </c>
       <c r="I15" t="n">
-        <v>0.823</v>
+        <v>2.8372</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1553</v>
+        <v>0.6675</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9075</v>
+        <v>-2.7519</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2479</v>
+        <v>3.4193</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3538</v>
+        <v>-1.026</v>
       </c>
       <c r="N15" t="n">
-        <v>0.07099999999999999</v>
+        <v>-0.4439</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4248</v>
+        <v>-0.5821</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8556</v>
+        <v>3.4793</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7178</v>
+        <v>-0.9414</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.326</v>
+        <v>-0.6247</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3918</v>
+        <v>-0.3167</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2836</v>
+        <v>1.0722</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1804</v>
+        <v>0.8259</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8123</v>
+        <v>0.2226</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3681</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>1.3069</v>
@@ -1702,13 +1702,13 @@
         <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1419</v>
+        <v>-0.4964</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6097</v>
+        <v>0.02</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7516</v>
+        <v>-0.5164</v>
       </c>
       <c r="V16" t="n">
         <v>-1.6083</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6431</v>
+        <v>0.5517</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5365</v>
+        <v>0.8902</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1066</v>
+        <v>-0.3385</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2935</v>
+        <v>-0.6251</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-0.9832</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2142</v>
+        <v>0.3581</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2894</v>
+        <v>-0.1352</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3998</v>
+        <v>-0.3929</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1104</v>
+        <v>0.2576</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.004</v>
+        <v>-0.4899</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1078</v>
+        <v>-0.5904</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1038</v>
+        <v>0.1005</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6237</v>
+        <v>2.5515</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6237</v>
+        <v>2.5515</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9212</v>
+        <v>-0.6967</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8259</v>
+        <v>-0.0468</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0953</v>
+        <v>-0.6499</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.6083</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.6083</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0387</v>
+        <v>0.0197</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1291</v>
+        <v>-0.0533</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0904</v>
+        <v>0.073</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1063</v>
+        <v>-0.2935</v>
       </c>
       <c r="H18" t="n">
-        <v>0.168</v>
+        <v>-0.5076000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2743</v>
+        <v>0.2142</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.08110000000000001</v>
+        <v>-0.2894</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2283</v>
+        <v>-0.3998</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1472</v>
+        <v>0.1104</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0252</v>
+        <v>-0.004</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3963</v>
+        <v>-0.1078</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4216</v>
+        <v>0.1038</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1372</v>
+        <v>0.2978</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2715</v>
+        <v>0.2361</v>
       </c>
       <c r="U18" t="n">
-        <v>1.8657</v>
+        <v>0.0617</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.6083</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2133</v>
+        <v>-1.2492</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1482</v>
+        <v>-2.365</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9349</v>
+        <v>1.1158</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3585</v>
+        <v>-0.1063</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.1958</v>
+        <v>0.168</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8372</v>
+        <v>-0.2743</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6675</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.7519</v>
+        <v>-0.2283</v>
       </c>
       <c r="L19" t="n">
-        <v>3.4193</v>
+        <v>0.1472</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.026</v>
+        <v>-0.0252</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4439</v>
+        <v>0.3963</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5821</v>
+        <v>-0.4216</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q19" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R19" t="n">
-        <v>3.4793</v>
+        <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.0867</v>
+        <v>0.9267</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.5683</v>
+        <v>0.0356</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5184</v>
+        <v>0.8911</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0722</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5398</v>
+        <v>-1.6742</v>
       </c>
       <c r="E20" t="n">
         <v>-1.6045</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06469999999999999</v>
+        <v>-0.0697</v>
       </c>
       <c r="G20" t="n">
         <v>-0.829</v>
@@ -2014,13 +2014,13 @@
         <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0149</v>
+        <v>-0.1494</v>
       </c>
       <c r="T20" t="n">
         <v>-0.2987</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2838</v>
+        <v>0.1494</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9955</v>
+        <v>-2.44</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7783</v>
+        <v>-2.4244</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2172</v>
+        <v>-0.0155</v>
       </c>
       <c r="G21" t="n">
         <v>0.5454</v>
@@ -2092,13 +2092,13 @@
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7934</v>
+        <v>-0.2379</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5149</v>
+        <v>-0.161</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2785</v>
+        <v>-0.0769</v>
       </c>
       <c r="V21" t="n">
         <v>-1.3558</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2287</v>
+        <v>-4.0835</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.1636</v>
+        <v>-5.22</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9349</v>
+        <v>1.1365</v>
       </c>
       <c r="G22" t="n">
         <v>-3.3765</v>
@@ -2170,13 +2170,13 @@
         <v>3.0154</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.012</v>
+        <v>-0.8667</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4936</v>
+        <v>-0.55</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5184</v>
+        <v>-0.3167</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5361</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2463</v>
+        <v>-1.246399999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.812200000000001</v>
+        <v>-7.811999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>6.5658</v>
+        <v>6.565699999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>2.0702</v>
+        <v>2.070200000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8402000000000001</v>
+        <v>-0.8402000000000005</v>
       </c>
       <c r="I23" t="n">
         <v>2.910399999999999</v>
@@ -2224,7 +2224,7 @@
         <v>3.8595</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6563000000000001</v>
+        <v>-0.6562999999999994</v>
       </c>
       <c r="L23" t="n">
         <v>4.5158</v>
@@ -2248,13 +2248,13 @@
         <v>17.3965</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.4398</v>
+        <v>-3.439799999999999</v>
       </c>
       <c r="T23" t="n">
         <v>-2.2185</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2212</v>
+        <v>-1.2211</v>
       </c>
       <c r="V23" t="n">
         <v>-5.6757</v>
